--- a/public/StructureDefinition-pghd-activity.xlsx
+++ b/public/StructureDefinition-pghd-activity.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-activity.xlsx
+++ b/public/StructureDefinition-pghd-activity.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
